--- a/data_extactor/batch_10_fa/batch_0062_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0062_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>پایگاه‌های داده اطلاعات مشتریان | نرم‌افزار تصویرسازی داده‌ها | Facebook | نرم‌افزار حسابداری مالی | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Structured query language SQL | Tableau | سیستم مدیریت محتوای آژانس مسافرتی | نرم‌افزار مرورگر وب</t>
+          <t>پایگاه‌های داده اطلاعات مشتریان | نرم‌افزار تجسم داده | Facebook | نرم‌افزار حسابداری مالی | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | زبان پرس‌وجوی ساختاریافته SQL | Tableau | سیستم مدیریت محتوای آژانس مسافرتی | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | گوش‌دادن فعالانه | درک مطلب خوانده‌شده | نگارش | تفکر انتقادی | یادگیری فعالانه | پایش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | فروش و بازاریابی | امور اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک مطلب نوشته‌شده | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | ترتیب‌دهی به اطلاعات | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی | بیان مکتوب | بینایی دور | تقسیم زمان | توجه انتخابی | خلاقیت و ابتکار</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | بینایی دور | تقسیم توجه | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | ایمیل | دفعات تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم به‌طور کلی | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان | نامه‌ها و یادداشت‌های مکتوب | محیط‌های داخلی، دارای کنترل دما | صرف زمان به صورت نشسته</t>
+          <t>مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | ایمیل | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متصدیان شهربازی و تفریحات | باربران چمدان و پادوهای هتل | رانندگان اتوبوس، ترانزیت و بین‌شهری | دربان‌ها و راهنمایان هتل | متصدیان باجه و اجاره | نمایندگان خدمات مشتریان | مدیران سرگرمی و تفریحات، به‌جز قمار | سرپرستان رده اول کارکنان سرگرمی و تفریحات، به‌جز خدمات قمار | مهمانداران هواپیما | کارگزاران حمل‌ونقل کالا | مدیران اقامتگاه‌ها | برنامه‌ریزان جلسات، کنوانسیون‌ها و رویدادها | اپراتورهای قایق‌های موتوری | طبیعت‌شناسان پارک | متصدیان مسافران | کارکنان تفریحات | نمایندگان رزرو و بلیط حمل‌ونقل و متصدیان سفر | راهنمایان تور و همراهان | آژانس‌های مسافرتی | راهنمایان سالن، متصدیان لابی و بلیط‌فروش‌ها</t>
+          <t>متصدیان تفریح و سرگرمی | باربران چمدان و پادوهای هتل | رانندگان اتوبوس، ترانزیت و بین‌شهری | کانسرج‌ها | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | مدیران سرگرمی و تفریح، به جز قماربازی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | مهمانداران هواپیما | متصدیان حمل و نقل | مدیران اقامتی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | اپراتورهای قایق موتوری | طبیعت‌شناسان پارک | متصدیان مسافران | کارکنان تفریحات | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | راهنمایان تور و همراهان | آژانس‌های مسافرتی | راهنماها، متصدیان لابی و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>پایش | گوش‌دادن فعالانه | سخن‌گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعالانه | نگارش | درک مطلب خوانده‌شده</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | آموزش و تربیت | ایمنی و امنیت عمومی | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | بینایی دور | استدلال قیاسی | درک مطلب نوشته‌شده | بینایی نزدیک | تقسیم زمان | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | ترتیب‌دهی به اطلاعات | وضوح گفتار | استدلال استقرایی | روان بودن ایده‌ها | بیان مکتوب</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | بینایی دور | استدلال قیاسی | درک کتبی | بینایی نزدیک | تقسیم توجه | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | وضوح گفتار | استدلال استقرایی | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | محیط‌های داخلی، دارای کنترل دما | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان به صورت ایستاده | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان برای ایستادن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران آموزشی، از پیش‌دبستانی تا متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | سرپرستان رده اول کارکنان خدمات شخصی | متخصصان آموزش سلامت | دستیاران سلامت در منزل | معلمان مهدکودک، به‌جز آموزش استثنایی | مدیران خدمات پزشکی و بهداشتی | پرستاران بچه | دستیاران پرستاری | دستیاران مراقبت شخصی | معلمان پیش‌دبستانی، به‌جز آموزش استثنایی | مدیران خدمات اجتماعی و جامعه | معلمان آموزش استثنایی، دبستان | معلمان آموزش استثنایی، مهدکودک | معلمان آموزش استثنایی، دوره اول متوسطه | معلمان آموزش استثنایی، پیش‌دبستانی | معلمان آموزش استثنایی، دوره دوم متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، متوسطه اول و دوم، به‌جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | سرپرستان خط اول کارگران خدمات شخصی | متخصصان آموزش بهداشت | کمک‌یاران سلامت در منزل | مربیان کودکستان، به استثنای آموزش استثنایی | مدیران خدمات پزشکی و بهداشتی | پرستاران بچه در منزل | کمک‌پرستاران | کمک‌یاران مراقبت شخصی | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | مدیران خدمات اجتماعی و جامعه | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>پایش | گوش‌دادن فعالانه | سخن‌گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعالانه | نگارش | درک مطلب خوانده‌شده</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مشتری‌مداری و خدمات شخصی | روان‌شناسی | آموزش و تربیت | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | درک مطلب نوشته‌شده | بینایی نزدیک | توجه انتخابی | خلاقیت و ابتکار | روان بودن ایده‌ها | بیان مکت | قدرت بدنی بالاتنه | ترتیب‌دهی به اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | درک کتبی | بینایی نزدیک | توجه انتخابی | اصالت | روانی ایده‌ها | بیان کتبی | قدرت تنه | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و در تیم‌ها | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | ارتباط با دیگران | در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به صورت ایستاده | قرار گرفتن در معرض صداها و سطوحی از نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط‌های داخلی، دارای کنترل دما | محیط‌های بیرونی، در معرض تمامی شرایط آب و هوایی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | ارتباط با دیگران | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | فضای باز، در معرض تمام شرایط آب و هوایی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان و کارکنان مراقبت از کودکان | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | سرپرستان رده اول کارکنان خدمات شخصی | مددکاران اجتماعی حوزه سلامت | دستیاران سلامت در منزل | معلمان مهدکودک، به‌جز آموزش استثنایی | پرستاران عملی دارای مدرک و پرستاران حرفه‌ای دارای مدرک | ماماها | دستیاران پرستاری | کاردرمانگران | دستیاران کاردرمانی | دستیاران مراقبت شخصی | معلمان پیش‌دبستانی، به‌جز آموزش استثنایی | دستیاران روان‌پزشکی | پرستاران ثبت‌نام شده | مشاوران خوابگاه | دستیاران خدمات اجتماعی و انسانی | معلمان آموزش استثنایی، پیش‌دبستانی | دستیاران آموزشی، آموزش استثنایی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان و کارکنان مراقبت از کودکان | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | سرپرستان خط اول کارگران خدمات شخصی | مددکاران اجتماعی مراقبت‌های بهداشتی | کمک‌یاران سلامت در منزل | مربیان کودکستان، به استثنای آموزش استثنایی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | ماماها | کمک‌پرستاران | کاردرمانگران | دستیاران کاردرمانی | کمک‌یاران مراقبت شخصی | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | کمک‌یاران روان‌پزشکی | پرستاران ثبت‌شده | مشاوران خوابگاه و اقامتگاه | دستیاران خدمات اجتماعی و انسانی | معلمان آموزش ویژه، پیش‌دبستانی | دستیاران آموزشی، آموزش استثنایی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | گوش‌دادن فعالانه | راهبردهای یادگیری | پایش | یادگیری فعالانه | تفکر انتقادی | درک مطلب خوانده‌شده</t>
+          <t>سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | نظارت | یادگیری فعال | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | آموزش و تربیت | زبان انگلیسی | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استقامت بدنی | انعطاف‌پذیری حرکتی | هماهنگی کلی بدن | بیان شفاهی | قدرت بدنی بالاتنه | وضوح گفتار | قدرت پویا | قدرت ایستا | روان بودن ایده‌ها | درک مطلب نوشته‌شده | درک شنیداری | قدرت انفجاری | هماهنگی چندعضوی | زبردستی دستی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | خلاقیت و ابتکار | تشخیص گفتار | بینایی دور | بینایی نزدیک | تعادل کلی بدن | انعطاف‌پذیری پویا</t>
+          <t>استقامت | انعطاف‌پذیری دامنه حرکت | هماهنگی کلی بدن | بیان شفاهی | قدرت تنه | وضوح گفتار | قدرت پویا | قدرت ایستا | روانی ایده‌ها | درک کتبی | درک شفاهی | قدرت انفجاری | هماهنگی چند عضو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | اصالت | تشخیص گفتار | بینایی دور | بینایی نزدیک | تعادل کلی بدن | انعطاف‌پذیری پویا</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>محیط‌های داخلی، دارای کنترل دما | گفتگوهای چهره‌به‌چهره با افراد و در تیم‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | صرف زمان به صورت ایستاده | تعامل با مشتریان خارجی یا عموم مردم به‌طور کلی | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | ایمیل | صرف زمان برای خم شدن یا چرخاندن بدن | دفعات تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سخنرانی عمومی | مکالمات تلفنی | قرار گرفتن در معرض صداها و سطوحی از نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای انجام حرکات تکراری | سطح رقابت | سلامت و ایمنی سایر کارکنان | صرف زمان برای پیاده‌روی یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | ایمیل | صرف زمان برای خم کردن یا چرخاندن بدن | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سخنرانی عمومی | مکالمات تلفنی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای انجام حرکات تکراری | سطح رقابت | سلامت و ایمنی سایر کارکنان | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی تطبیقی | مربیان حیوانات | مربیان ورزشی | مربیان و استعداد‌یاب‌ها | متخصصان تغذیه و رژیم‌درمانی | فیزیولوژیست‌های ورزشی | هماهنگ‌کنندگان تناسب اندام و تندرستی | متخصصان آموزش سلامت | کاردرمانگران | دستیاران کاردرمانی | دستیاران کاردرمانی | دستیاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپ‌ها | کارکنان تفریحات | مدرسان مطالعات تفریحی و تناسب اندام، پس از متوسطه | درمانگران تفریحی | معلمان خودشکوفایی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
+          <t>متخصصان تربیت بدنی تطبیقی | مربیان حیوانات | مربیان ورزشی | مربیان و استعدادیاب‌ها | متخصصان رژیم غذایی و تغذیه | فیزیولوژیست‌های ورزشی | هماهنگ‌کنندگان تناسب اندام و سلامتی | متخصصان آموزش بهداشت | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کارکنان تفریحات | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | درمانگران تفریحی | معلمان خودسازی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Appletree | Corel WordPerfect Office Suite | نرم‌افزار پایگاه داده | GroupMe | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Windows | Microsoft Word | نرم‌افزار بایگانی سوابق | نرم‌افزار زمان‌بندی | YouTube</t>
+          <t>Appletree | Corel WordPerfect Office Suite | نرم‌افزار پایگاه داده | GroupMe | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Windows | Microsoft Word | نرم‌افزار ثبت سوابق | نرم‌افزار زمان‌بندی | YouTube</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | گوش‌دادن فعالانه | پایش | تفکر انتقادی | راهبردهای یادگیری | درک مطلب خوانده‌شده | نگارش | یادگیری فعالانه</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ایمنی و امنیت عمومی | مشتری‌مداری و خدمات شخصی | آموزش و تربیت | قانون و دولت | روان‌شناسی | امور اداری | کامپیوتر و الکترونیک | ریاضیات</t>
+          <t>زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | آموزش و پرورش | قانون و دولت | روان‌شناسی | اداری | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | درک مطلب نوشته‌شده | استدلال قیاسی | انعطاف‌پذیری در دسته‌بندی | ترتیب‌دهی به اطلاعات | خلاقیت و ابتکار | روان بودن ایده‌ها | بیان مکتوب | بینایی دور | تقسیم زمان | توجه انتخابی | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | درک کتبی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها | بیان کتبی | بینایی دور | تقسیم توجه | توجه انتخابی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و در تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | محیط‌های داخلی، دارای کنترل دما | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | دفعات تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض صداها و سطوحی از نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | تعامل با مشتریان خارجی یا عموم مردم به‌طور کلی | برخورد با افراد نامطبوع، عصبانی یا بی‌ادب</t>
+          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعامل با مشتریان خارجی یا عموم مردم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | کارکنان بهداشت جامعه | مدیران فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی، از پیش‌دبستانی تا متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان تحصیلی، تربیتی و شغلی | مدیران سرگرمی و تفریحات، به‌جز قمار | سرپرستان رده اول کارکنان سرگرمی و تفریحات, به‌جز خدمات قمار | سرپرستان رده اول کارکنان خدمات شخصی | هماهنگ‌کنندگان تناسب اندام و تندرستی | متخصصان آموزش سلامت | هماهنگ‌کنندگان آموزشی | مدرسان مطالعات تفریحی و تناسب اندام، پس از متوسطه | درمانگران تفریحی | مشاوران توانبخشی | مشاوران خوابگاه | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران سلامت جامعه | مدیران، فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | مدیران سرگرمی و تفریح، به جز قماربازی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران خدمات شخصی | هماهنگ‌کنندگان تناسب اندام و سلامتی | متخصصان آموزش بهداشت | هماهنگ‌کنندگان آموزشی | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | درمانگران تفریحی | مشاوران توانبخشی | مشاوران خوابگاه و اقامتگاه | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعالانه | سخن‌گفتن | پایش | تفکر انتقادی | درک مطلب خوانده‌شده | یادگیری فعالانه | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | مدیریت و اداره امور | ایمنی و امنیت عمومی | آموزش و تربیت | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | امور اداری | پرسنل و منابع انسانی | درمان و مشاوره | روان‌شناسی | ارتباطات و رسانه | کامپیوتر و الکترونیک | قانون و دولت</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | ایمنی و امنیت عمومی | آموزش و پرورش | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | اداری | پرسنل و منابع انسانی | درمان و مشاوره | روان‌شناسی | ارتباطات و رسانه | رایانه و الکترونیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | درک مطلب نوشته‌شده | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان مکتوب | بینایی دور | توجه انتخابی | ترتیب‌دهی به اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | درک کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | بینایی دور | توجه انتخابی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | موقعیت‌های پرتننش | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط‌های داخلی، دارای کنترل دما | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | دفعات تصمیم‌گیری | اهمیت دقیق یا درست بودن</t>
+          <t>ایمیل | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی، از پیش‌دبستانی تا متوسطه | مدیران آموزشی، پس از متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان تحصیلی، تربیتی و شغلی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | سرپرستان رده اول کارکنان سرگرمی و تفریحات، به‌جز خدمات قمار | سرپرستان رده اول کارکنان خانه‌داری و سرایداری | سرپرستان رده اول کارکنان خدمات شخصی | متخصصان آموزش سلامت | دستیاران سلامت در منزل | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | نمایندگان بیمار | دستیاران مراقبت شخصی | کارکنان تفریحات | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران، فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران خدمات شخصی | متخصصان آموزش بهداشت | کمک‌یاران سلامت در منزل | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | نمایندگان بیمار | کمک‌یاران مراقبت شخصی | کارکنان تفریحات | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت کامپیوتری تعمیر و نگهداری CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعالانه | سخن‌گفتن | درک مطلب خوانده‌شده | تفکر انتقادی | پایش | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | روان‌شناسی | آموزش و تربیت | ایمنی و امنیت عمومی | درمان و مشاوره</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | ایمنی و امنیت عمومی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | استدلال قیاسی | استدلال استقرایی | درک مطلب نوشته‌شده | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | تقسیم زمان | زبردستی انگشتان | زبردستی دستی | بینایی دور | به خاطرسپاری | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم به‌طور کلی | گفتگوهای چهره‌به‌چهره با افراد و در تیم‌ها | نزدیکی فیزیکی | صرف زمان به صورت ایستاده | صرف زمان برای پیاده‌روی یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط‌های داخلی، دارای کنترل دما | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد نامطبوع، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | دفعات تصمیم‌گیری | آزادی در تصمیم‌گیری</t>
+          <t>ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دستیاران مراقبت شخصی | دستیاران سلامت در منزل | مربیان و کارکنان مراقبت از کودکان | پرستاران بچه | مشاوران خوابگاه | کارکنان تفریحات | مربیان ورزشی و مدرسان تناسب اندام گروهی | مراقبان حیوانات | مربیان حیوانات | دربان‌ها و راهنمایان هتل | راهنمایان تور و همراهان | راهنمایان سفر | آرایشگران مردانه | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | متخصصان مراقبت از پوست | مانیکوریست‌ها و پدیکوریست‌ها | ماساژورها | دستیاران پرستاری | دستیاران خدمات اجتماعی و انسانی | سرپرستان رده اول کارکنان خدمات شخصی</t>
+          <t>کمک‌یاران مراقبت شخصی | کمک‌یاران سلامت در منزل | مربیان و کارکنان مراقبت از کودکان | پرستاران بچه در منزل | مشاوران خوابگاه و اقامتگاه | کارکنان تفریحات | مربیان ورزشی و مدرسان تناسب اندام گروهی | مراقبان حیوانات | مربیان حیوانات | کانسرج‌ها | راهنمایان تور و همراهان | راهنمایان سفر | آرایشگران مردانه | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | متخصصان مراقبت از پوست | مانیکوریست‌ها و پدیکوریست‌ها | ماساژدرمانگران | کمک‌پرستاران | دستیاران خدمات اجتماعی و انسانی | سرپرستان خط اول کارگران خدمات شخصی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعالانه | سخن‌گفتن | تفکر انتقادی | پایش | راهبردهای یادگیری | یادگیری فعالانه | نگارش | درک مطلب خوانده‌شده</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | مدیریت و اداره امور | فروش و بازاریابی | زبان انگلیسی | آموزش و تربیت | پرسنل و منابع انسانی | ریاضیات | کامپیوتر و الکترونیک | اقتصاد و حسابداری | امور اداری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | فروش و بازاریابی | زبان انگلیسی | آموزش و پرورش | پرسنل و منابع انسانی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک شنیداری | بیان شفاهی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی به اطلاعات | استدلال قیاسی | خلاقیت و ابتکار | روان بودن ایده‌ها | بیان مکتوب | درک مطلب نوشته‌شده | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی</t>
+          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال قیاسی | اصالت | روانی ایده‌ها | بیان کتبی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و در تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط‌های داخلی، دارای کنترل دما | تعامل با مشتریان خارجی یا عموم مردم به‌طور کلی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | دفعات تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت ایستاده | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | برخورد با افراد نامطبوع، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های مکتوب | موقعیت‌های پرتننش</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | صندوق‌داران | متصدیان باجه و اجاره | نمایندگان خدمات مشتریان | سرپرستان رده اول کارکنان سرگرمی و تفریحات، به‌جز خدمات قمار | سرپرستان رده اول کارکنان تهیه و سرو غذا | سرپرستان رده اول دستیاران، کارگران و جابجاکنندگان دستی مواد | سرپرستان رده اول کارکنان خانه‌داری و سرایداری | سرپرستان رده اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان رده اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده اول کارکنان پشتیبانی اداری و دفتری | سرپرستان رده اول متصدیان مسافران | سرپرستان رده اول کارکنان خدمات شخصی | سرپرستان رده اول کارکنان تولید و عملیات | مدیران کل و عملیاتی | فروشندگان خرده‌فروشی | مدیران فروش | نمایندگان فروش خدمات، به‌جز تبلیغات، بیمه، خدمات مالی و سفر | قفسه‌چین‌ها و پرکننده‌های سفارش</t>
+          <t>مدیران خدمات اداری | صندوق‌داران | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان رده اول کارگران تولید و بهره‌برداری | مدیران عمومی و عملیات | فروشندگان خرده‌فروشی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | قفسه‌چین‌ها و پرکننده‌های سفارش</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار بودجه‌بندی | Cisco Webex | پایگاه‌های داده اطلاعات مشتریان | Delphi Discovery | Delphi Technology | نرم‌افزار تبادل الکترونیکی داده‌ها EDI | نرم‌افزار حسابداری مالی | نرم‌افزار نمودار جریان | نرم‌افزار ارتباطات ابری و همکاری Fuze | نرم‌افزار ساخت گرافیک | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | NetSuite ERP | نرم‌افزار جلسات آنلاین | Oracle Eloqua | نرم‌افزار مدیریت کسب‌وکار QuickBase | نرم‌افزار SAP | نرم‌افزار Salesforce | Salesforce.com Salesforce CRM | SugarCRM Sugar UX | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار | YouTube</t>
+          <t>نرم‌افزار بودجه‌بندی | Cisco Webex | پایگاه‌های داده اطلاعات مشتریان | Delphi Discovery | Delphi Technology | نرم‌افزار تبادل الکترونیکی داده EDI | نرم‌افزار حسابداری مالی | نرم‌افزار نمودار جریان | نرم‌افزار ارتباطات ابری و همکاری Fuze | نرم‌افزار ایجاد گرافیک | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | NetSuite ERP | نرم‌افزار جلسات آنلاین | Oracle Eloqua | نرم‌افزار مدیریت کسب‌وکار QuickBase | نرم‌افزار SAP | نرم‌افزار Salesforce | Salesforce.com Salesforce CRM | SugarCRM Sugar UX | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار | YouTube</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>پایش | سخن‌گفتن | گوش‌دادن فعالانه | درک مطلب خوانده‌شده | نگارش | تفکر انتقادی | یادگیری فعالانه | راهبردهای یادگیری | ریاضیات</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | مدیریت و اداره امور | زبان انگلیسی | پرسنل و منابع انسانی | اقتصاد و حسابداری | فروش و بازاریابی | ریاضیات | آموزش و تربیت</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | پرسنل و منابع انسانی | اقتصاد و حسابداری | فروش و بازاریابی | ریاضیات | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک مطلب نوشته‌شده | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | بینایی نزدیک | انعطاف‌پذیری در دسته‌بندی | حساسیت به مسئله | روان بودن ایده‌ها | بیان مکتوب | استدلال ریاضی | سهولت در کار با اعداد</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | روانی ایده‌ها | بیان کتبی | استدلال ریاضی | توانایی عددی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و در تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط‌های داخلی, دارای کنترل دما | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | دفعات تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم به‌طور کلی | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های مکتوب | صرف زمان به صورت نشسته | اهمیت تکرار وظایف یکسان | سلامت و ایمنی سایر کارکنان | سطح رقابت | موقعیت‌های پرتننش</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | سلامت و ایمنی سایر کارکنان | سطح رقابت | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | نمایندگان خدمات مشتریان | سرپرستان رده اول کارکنان ساختمانی و استخراج | سرپرستان رده اول کارکنان سرگرمی و تفریحات، به‌جز خدمات قمار | سرپرستان رده اول کارکنان تهیه و سرو غذا | سرپرستان رده اول دستیاران، کارگران و جابجاکنندگان دستی مواد | سرپرستان رده اول کارکنان خانه‌داری و سرایداری | سرپرستان رده اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان رده اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان رده اول کارکنان پشتیبانی اداری و دفتری | سرپرستان رده اول متصدیان مسافران | سرپرستان رده اول کارکنان خدمات شخصی | سرپرستان رده اول کارکنان تولید و عملیات | سرپرستان رده اول کارکنان فروش خرده‌فروشی | سرپرستان رده اول کارکنان امنیتی | مدیران کل و عملیاتی | متخصصان منابع انسانی | تحلیلگران مدیریت | مدیران فروش | نمایندگان فروش خدمات، به‌جز تبلیغات، بیمه، خدمات مالی و سفر</t>
+          <t>مدیران خدمات اداری | نمایندگان خدمات مشتریان | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان رده اول کارکنان فروش خرده‌فروشی | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیات | متخصصان منابع انسانی | تحلیل‌گران مدیریت | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AFEXDirect | Apple Safari | نرم‌افزار دفترداری | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار دستگاه‌های کامپیوتر جیبی | Microsoft Edge | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Mozilla Firefox | ReliaSoft Prism</t>
+          <t>AFEXDirect | Apple Safari | نرم‌افزار حسابداری | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار دستگاه‌های کامپیوتر جیبی | Microsoft Edge | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Mozilla Firefox | ReliaSoft Prism</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | گوش‌دادن فعالانه</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | بینایی نزدیک | وضوح گفتار | درک مطلب نوشته‌شده | حساسیت به مسئله | تشخیص گفتار | ترتیب‌دهی به اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | درک کتبی | حساسیت به مسئله | تشخیص گفتار | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و در تیم‌ها | مکالمات تلفنی | برخورد با افراد نامطبوع، عصبانی یا بی‌ادب | صرف زمان به صورت ایستاده | دفعات تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط‌های داخلی، دارای کنترل دما | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم به‌طور کلی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورت‌حساب و ثبت | متصدیان باجه و اجاره | نمایندگان خدمات مشتریان | کارکنان فروش خانه‌به‌خانه، فروشندگان روزنامه و دستفروشان خیابانی و کارکنان مرتبط | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده اول کارکنان فروش خرده‌فروشی | کارکنان قفس بازی‌های کازینو | تعویض‌کنندگان پول بازی و صندوق‌داران باجه | کارمندان پذیرش هتل، متل و تفریحگاه | کارمندان افتتاح حساب جدید | کارمندان دفتری عمومی | کارمندان ثبت سفارش | دستیاران داروخانه | کارمندان پست | متصدیان پذیرش و اطلاعات | فروشندگان خرده‌فروشی | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | بازاریابان تلفنی | تحویل‌داران بانک</t>
+          <t>کارمندان صدور صورتحساب و ثبت | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده اول کارکنان فروش خرده‌فروشی | کارکنان باجه قمارخانه | صندوق‌داران غرفه و مسئولان پول خرد قماربازی | کارمندان پذیرش هتل، متل و اقامتگاه | کارمندان حساب‌های جدید | کارمندان دفتری عمومی | کارمندان ثبت سفارش | دستیاران داروخانه | کارمندان خدمات پستی | متصدیان پذیرش و کارمندان اطلاعات | فروشندگان خرده‌فروشی | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | بازاریابان تلفنی | تحویل‌داران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0062_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0062_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | دید نزدیک | استدلال قیاسی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی | بیان کتبی | دید دور | تقسیم توجه | توجه انتخابی | ابتکار و اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | بینایی دور | تقسیم توجه | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی‌ها | باربران هتل و حمل‌کنندگان چمدان | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | راهنمایان تشریفات و خدمات هتل | کارمندان پذیرش، باجه و اجاره کالا | کارشناسان خدمات مشتریان | مدیران امور تفریحی و سرگرمی | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی | مهمانداران هواپیما | متصدیان حمل‌ونقل کالا و بارفرابران | مدیران مراکز اقامتی و هتل‌ها | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | قایق‌رانان قایق‌های موتوری | کارشناسان و راهنمایان طبیعت‌شناسی پارک‌ها | مهمانداران مسافران | کارکنان امور تفریحی و اوقات فراغت | متصدیان صدور بلیت و کارمندان رزرواسیون سفر | راهنمایان تور و همراهان گردشگران | کارشناسان و دفاتر خدمات مسافرتی | راهنمایان سالن، متصدیان لابی و کنترل‌کنندگان بلیت</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | متصدیان حمل بار و خدمات هتل | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | متصدیان تشریفات و خدمات میهمانان | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | مدیران مجموعه‌های تفریحی، ورزشی و رویدادها | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | مهمانداران هواپیما | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | مدیران هتل و مراکز اقامتی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | قایقرانان قایق‌های موتوری | طبیعت‌شناسان و کارشناسان پارک‌های ملی | مهمانداران و متصدیان خدمات مسافران | کارکنان و متصدیان امور تفریحی و اوقات فراغت | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | راهنمایان تور و گردشگری | کارشناسان و دفاتر خدمات مسافرتی و جهانگردی | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و تدریس | ایمنی و امنیت عمومی | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | دید دور | استدلال قیاسی | درک کتبی | دید نزدیک | تقسیم توجه | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | وضوح گفتار | استدلال استقرایی | روانی و سیالی ایده‌ها | بیان کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | بینایی دور | استدلال قیاسی | درک کتبی | بینایی نزدیک | تقسیم توجه | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | وضوح گفتار | استدلال استقرایی | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران آموزشی دوره‌های پیش‌دبستانی تا متوسطه | مدیران مراکز پیش‌دبستانی و مهدکودک‌ها | سرپرستان رده‌اول کارکنان خدمات فردی | کارشناسان آموزش بهداشت و ارتقای سلامت | مراقبان سلامت در منزل | آموزگاران دوره آمادگی و مهدکودک | مدیران خدمات بهداشتی و درمانی | پرستاران خانگی و دایه‌ها | کمک‌بهیاران و دستیاران پرستاری | مراقبان خدمات فردی | مربیان پیش‌دبستانی | مدیران خدمات اجتماعی و خدمات شهری | معلمان استثنایی مقطع ابتدایی | معلمان استثنایی دوره مهدکودک و آمادگی | معلمان استثنایی مقطع متوسطه اول | معلمان استثنایی مقطع پیش‌دبستانی | معلمان استثنایی مقطع متوسطه دوم | کمک‌آموزگاران مدارس | کمک‌آموزگاران آموزش و پرورش استثنایی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | کارشناسان آموزش بهداشت و ارتقای سلامت | مراقبان سلامت و بهیاران مراقبت در منزل | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | مدیران خدمات درمانی و بهداشتی | پرستاران خانگی و دایه‌ها | کمک‌پرستاران | مراقبان خدمات شخصی و همراهان توان‌خواهان | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | مدیران خدمات اجتماعی و خدمات مردمی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی | آموزش و تدریس | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | درک کتبی | دید نزدیک | توجه انتخابی | ابتکار و اصالت | روانی و سیالی ایده‌ها | بیان کتبی | قدرت تنه | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | درک کتبی | بینایی نزدیک | توجه انتخابی | اصالت | روانی ایده‌ها | بیان کتبی | قدرت تنه | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان و مراقبان کودک | مدیران مراکز پیش‌دبستانی و مهدکودک‌ها | سرپرستان رده‌اول کارکنان خدمات فردی | مددکاران اجتماعی بخش درمان و سلامت | مراقبان سلامت در منزل | آموزگاران دوره آمادگی و مهدکودک | بهیاران و کمک‌پرستاران دارای مجوز | ماماها | کمک‌بهیاران و دستیاران پرستاری | کاردرمانگران | دستیاران کاردرمانی | مراقبان خدمات فردی | مربیان پیش‌دبستانی | کمک‌یاران بخش روان‌پزشکی | پرستاران دارای پروانه | مربیان و سرپرستان خوابگاه | دستیاران خدمات اجتماعی و انسانی | معلمان استثنایی مقطع پیش‌دبستانی | کمک‌آموزگاران آموزش و پرورش استثنایی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان و مراقبان کودک | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مددکاران اجتماعی بخش سلامت و درمان | مراقبان سلامت و بهیاران مراقبت در منزل | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | بهیاران و کمک‌پرستاران دارای مجوز | ماماهای پرستار | کمک‌پرستاران | کاردرمانگران | کاردان‌های کاردرمانی | مراقبان خدمات شخصی و همراهان توان‌خواهان | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | کمک‌یاران بخش روان‌پزشکی | پرستاران | سرپرستان و مشاوران خوابگاه | دستیاران خدمات اجتماعی و انسانی | معلمان آموزش استثنایی دوره پیش‌دبستانی | کمک‌معلمان آموزش استثنایی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | راهبردهای یادگیری | نظارت | یادگیری فعال | تفکر انتقادی | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | نظارت | یادگیری فعال | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | زبان انگلیسی | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استقامت بدنی | انعطاف‌پذیری عمومی بدن | هماهنگی کلی اعضای بدن | بیان شفاهی | قدرت تنه | وضوح گفتار | قدرت بدنی پویا | قدرت بدنی ایستا | روانی و سیالی ایده‌ها | درک کتبی | درک شفاهی | توان انفجاری | هماهنگی بین چند اندام | چابکی دستی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | ابتکار و اصالت | تشخیص گفتار | دید دور | دید نزدیک | تعادل کلی بدن | انعطاف‌پذیری پویا</t>
+          <t>استقامت | انعطاف‌پذیری دامنه حرکت | هماهنگی کلی بدن | بیان شفاهی | قدرت تنه | وضوح گفتار | قدرت پویا | قدرت ایستا | روانی ایده‌ها | درک کتبی | درک شفاهی | قدرت انفجاری | هماهنگی چند عضو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | اصالت | تشخیص گفتار | بینایی دور | بینایی نزدیک | تعادل کلی بدن | انعطاف‌پذیری پویا</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی تطبیقی و اصلاحی | مربیان آموزش حیوانات | مربیان تخصصی ورزش و سلامت | مربیان و استعدادیا Morten ورزش | متخصصان تغذیه و رژیم‌درمانی | فیزیولوژیست‌های ورزشی | هماهنگ‌کنندگان امور تناسب اندام و سلامت | کارشناسان آموزش بهداشت و ارتقای سلامت | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپ‌ها | کارکنان امور تفریحی و اوقات فراغت | مدرسان دانشگاهی تربیت بدنی و علوم ورزشی | متخصصان تفریح‌درمانی | مربیان آموزش‌های آزاد و مهارت‌های فردی | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>متخصصان تربیت بدنی انطباقی | مربیان و رام‌کنندگان حیوانات | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | مربیان و استعدادیابان ورزشی | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | فیزیولوژیست‌های ورزشی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | کارشناسان آموزش بهداشت و ارتقای سلامت | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | کارشناسان تفریح‌درمانی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | حقوق و مقررات دولتی | روان‌شناسی | امور اداری و دفتری | رایانه و الکترونیک | ریاضیات</t>
+          <t>زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | آموزش و پرورش | قانون و دولت | روان‌شناسی | اداری | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | درک کتبی | استدلال قیاسی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | ابتکار و اصالت | روانی و سیالی ایده‌ها | بیان کتبی | دید دور | تقسیم توجه | توجه انتخابی | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | درک کتبی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها | بیان کتبی | بینایی دور | تقسیم توجه | توجه انتخابی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | رابطان و کارشناسان بهداشت جامعه | مدیران فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی دوره‌های پیش‌دبستانی تا متوسطه | مدیران مراکز پیش‌دبستانی و مهدکودک‌ها | مشاوران و کارشناسان هدایت تحصیلی و شغلی | مدیران امور تفریحی و سرگرمی | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی | سرپرستان رده‌اول کارکنان خدمات فردی | هماهنگ‌کنندگان امور تناسب اندام و سلامت | کارشناسان آموزش بهداشت و ارتقای سلامت | هماهنگ‌کنندگان برنامه‌ریزی آموزشی | مدرسان دانشگاهی تربیت بدنی و علوم ورزشی | متخصصان تفریح‌درمانی | مشاوران توانبخشی | مربیان و سرپرستان خوابگاه | مدیران خدمات اجتماعی و خدمات شهری | دستیاران خدمات اجتماعی و انسانی | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | رابطان سلامت و بهورزان | مدیران فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، شغلی و هدایت استعدادها | مدیران مجموعه‌های تفریحی، ورزشی و رویدادها | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | کارشناسان آموزش بهداشت و ارتقای سلامت | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | سرپرستان و مشاوران خوابگاه | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ایمنی و امنیت عمومی | آموزش و تدریس | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | امور اداری و دفتری | امور اداری و منابع انسانی | درمان و مشاوره | روان‌شناسی | ارتباطات و رسانه | رایانه و الکترونیک | حقوق و مقررات دولتی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | ایمنی و امنیت عمومی | آموزش و پرورش | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | اداری | پرسنل و منابع انسانی | درمان و مشاوره | روان‌شناسی | ارتباطات و رسانه | رایانه و الکترونیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | درک کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان کتبی | دید دور | توجه انتخابی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | درک کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | بینایی دور | توجه انتخابی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی دوره‌های پیش‌دبستانی تا متوسطه | مدیران آموزش عالی و دانشگاهی | مدیران مراکز پیش‌دبستانی و مهدکودک‌ها | مشاوران و کارشناسان هدایت تحصیلی و شغلی | کارشناسان مصاحبه و تعیین واجدین شرایط در برنامه‌های دولتی | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی | سرپرستان رده‌اول کارکنان خدمات و امور نظافتی | سرپرستان رده‌اول کارکنان خدمات فردی | کارشناسان آموزش بهداشت و ارتقای سلامت | مراقبان سلامت در منزل | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | رابطان و مسئولان پیگیری حقوق بیماران | مراقبان خدمات فردی | کارکنان امور تفریحی و اوقات فراغت | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات شهری | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | کارشناسان آموزش بهداشت و ارتقای سلامت | مراقبان سلامت و بهیاران مراقبت در منزل | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کارشناسان امور بیماران و پذیرش | مراقبان خدمات شخصی و همراهان توان‌خواهان | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | روان‌شناسی | آموزش و تدریس | ایمنی و امنیت عمومی | درمان و مشاوره</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | ایمنی و امنیت عمومی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | تقسیم توجه | چابکی انگشتان | چابکی دستی | دید دور | حفظ کردن | روانی و سیالی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مراقبان خدمات فردی | مراقبان سلامت در منزل | مربیان و مراقبان کودک | پرستاران خانگی و دایه‌ها | سرپرستان و مشاوران خوابگاه | کارکنان امور تفریحی و اوقات فراغت | مربیان ورزش و آمادگی جسمانی گروهی | متصدیان نگهداری حیوانات | مربیان آموزش حیوانات | راهنمایان تشریفات و خدمات هتل | راهنمایان تور و همراهان گردشگران | راهنمایان گردشگری و تور | پیرایشگران مردانه | آرایشگران، متخصصان مو و زیبایی | متخصصان مراقبت از پوست | متصدیان آرایش دست و پا و ناخن‌کاران | ماساژورها و ماساژدرمانگران | کمک‌بهیاران و دستیاران پرستاری | دستیاران خدمات اجتماعی و انسانی | سرپرستان رده‌اول کارکنان خدمات فردی</t>
+          <t>مراقبان خدمات شخصی و همراهان توان‌خواهان | مراقبان سلامت و بهیاران مراقبت در منزل | مربیان و مراقبان کودک | پرستاران خانگی و دایه‌ها | سرپرستان و مشاوران خوابگاه | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مربیان ورزش و آمادگی جسمانی گروهی | مراقبان و نگهداران حیوانات | مربیان و رام‌کنندگان حیوانات | متصدیان تشریفات و خدمات میهمانان | راهنمایان تور و گردشگری | راهنمایان گردشگری و تور | پیرایشگران مردانه | آرایشگران و متخصصان زیبایی | متخصصان و تکنسین‌های مراقبت از پوست | ناخن‌کاران و متخصصان مانیکور و پدیکور | ماساژدرمانگران | کمک‌پرستاران | دستیاران خدمات اجتماعی و انسانی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | فروش و بازاریابی | زبان انگلیسی | آموزش و تدریس | امور اداری و منابع انسانی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | فروش و بازاریابی | زبان انگلیسی | آموزش و پرورش | پرسنل و منابع انسانی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | تشخیص گفتار | حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات | استدلال قیاسی | ابتکار و اصالت | روانی و سیالی ایده‌ها | بیان کتبی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی</t>
+          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال قیاسی | اصالت | روانی ایده‌ها | بیان کتبی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | صندوق‌داران | کارمندان پذیرش، باجه و اجاره کالا | کارشناسان خدمات مشتریان | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده، دستیاران و جابه‌جا‌کنندگان دستی کالا | سرپرستان رده‌اول کارکنان خدمات و امور نظافتی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران مسافران | سرپرستان رده‌اول کارکنان خدمات فردی | سرپرستان رده‌اول کارکنان تولید و عملیات | مدیران ارشد اجرایی و عملیاتی | فروشندگان خرده‌فروشی | مدیران فروش | کارشناسان فروش خدمات | انبارداران و متصدیان جمع‌آوری و چیدمان سفارش‌ها</t>
+          <t>مدیران خدمات اداری و پشتیبانی | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده اول کارگران تولید و عملیات | مدیران کل و مدیران عملیات | فروشندگان خرده‌فروشی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | متصدیان چیدمان و آماده‌سازی سفارش</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | امور اداری و منابع انسانی | اقتصاد و حسابداری | فروش و بازاریابی | ریاضیات | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | پرسنل و منابع انسانی | اقتصاد و حسابداری | فروش و بازاریابی | ریاضیات | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری در دسته‌بندی | حساسیت به مسئله | روانی و سیالی ایده‌ها | بیان کتبی | استدلال ریاضی | توانایی کار با اعداد</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | روانی ایده‌ها | بیان کتبی | استدلال ریاضی | توانایی عددی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان خدمات مشتریان | سرپرستان رده‌اول استادکاران ساختمانی و استخراج | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده، دستیاران و جابه‌جا‌کنندگان دستی کالا | سرپرستان رده‌اول کارکنان خدمات و امور نظافتی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران مسافران | سرپرستان رده‌اول کارکنان خدمات فردی | سرپرستان رده‌اول کارکنان تولید و عملیات | سرپرستان رده‌اول فروشندگان خرده‌فروشی | سرپرستان رده‌اول مأموران حفاظتی و حراست | مدیران ارشد اجرایی و عملیاتی | کارشناسان منابع انسانی | تحلیل‌گران مدیریت و بهبود فرآیندها | مدیران فروش | کارشناسان فروش خدمات</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول فروشندگان خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیات | کارشناسان منابع انسانی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | درک کتبی | حساسیت به مسئله | تشخیص گفتار | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | درک کتبی | حساسیت به مسئله | تشخیص گفتار | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان صدور و ثبت صورت‌حساب | کارمندان پذیرش، باجه و اجاره کالا | کارشناسان خدمات مشتریان | فروشندگان دوره‌گرد، دست‌فروشان و مشاغل مرتبط | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | متصدیان باجه‌های مالی | متصدیان باجه‌های پرداخت و تبدیل وجوه | متصدیان پذیرش هتل‌ها، متل‌ها و مجتمع‌های اقامتی | کارمندان افتتاح حساب | متصدیان امور اداری عمومی | کارمندان ثبت و پیگیری سفارش‌ها | کمک‌یاران داروخانه | کارکنان باجه‌های پستی | متصدیان پذیرش و اطلاع‌رسانی | فروشندگان خرده‌فروشی | کارمندان ارسال، تحویل و انبارداری کالا | انبارداران و متصدیان جمع‌آوری و چیدمان سفارش‌ها | کارشناسان بازاریابی تلفنی | تحویل‌داران و متصدیان باجه بانک</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | متصدیان باجه و خزانه‌داری مراکز بازی و سرگرمی | صندوق‌داران و متصدیان تبدیل ژتون و وجه در مراکز تفریحی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان افتتاح حساب | متصدیان امور دفتری و امور عمومی اداری | متصدیان ثبت و پیگیری سفارش‌ها | کمک‌متصدیان داروخانه | متصدیان باجه و امور پستی | متصدیان پذیرش و اطلاعات | فروشندگان خرده‌فروشی | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | کارشناسان بازاریابی تلفنی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
